--- a/data/trans_camb/P6904-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 23,77</t>
+          <t>-8,38; 24,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 19,49</t>
+          <t>-17,19; 17,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 38,75</t>
+          <t>8,28; 39,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 21,34</t>
+          <t>-24,07; 21,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 28,42</t>
+          <t>-16,96; 28,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 17,3</t>
+          <t>-24,23; 16,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 16,9</t>
+          <t>-9,41; 18,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 19,07</t>
+          <t>-10,69; 18,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 26,25</t>
+          <t>1,74; 26,79</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 58,12</t>
+          <t>-14,67; 59,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 45,66</t>
+          <t>-30,58; 37,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 94,51</t>
+          <t>14,99; 97,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 40,14</t>
+          <t>-32,72; 43,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,7; 56,04</t>
+          <t>-22,4; 57,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 34,19</t>
+          <t>-31,29; 33,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 36,37</t>
+          <t>-15,16; 38,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 39,89</t>
+          <t>-18,06; 36,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 56,86</t>
+          <t>2,84; 58,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 24,51</t>
+          <t>-3,66; 23,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 30,93</t>
+          <t>3,83; 30,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 29,61</t>
+          <t>3,42; 28,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 30,25</t>
+          <t>-8,42; 30,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 43,76</t>
+          <t>6,68; 42,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 34,62</t>
+          <t>1,76; 34,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 21,87</t>
+          <t>-1,25; 21,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 29,49</t>
+          <t>9,69; 31,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 26,4</t>
+          <t>7,04; 26,52</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 59,81</t>
+          <t>-6,68; 54,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 75,63</t>
+          <t>7,16; 73,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 71,59</t>
+          <t>5,94; 68,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 95,83</t>
+          <t>-16,09; 92,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 150,35</t>
+          <t>12,75; 137,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 110,88</t>
+          <t>3,26; 116,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 51,46</t>
+          <t>-2,23; 51,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,96; 70,54</t>
+          <t>19,59; 77,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 63,51</t>
+          <t>13,74; 65,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 14,75</t>
+          <t>-14,51; 16,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 15,59</t>
+          <t>-10,15; 16,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -3,69</t>
+          <t>-34,15; -1,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,42; -5,11</t>
+          <t>-42,21; -4,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 25,91</t>
+          <t>-11,23; 25,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 34,74</t>
+          <t>-18,35; 32,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 2,92</t>
+          <t>-19,7; 3,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 16,38</t>
+          <t>-6,07; 16,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 21,74</t>
+          <t>-18,45; 23,73</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 30,53</t>
+          <t>-23,83; 33,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 31,59</t>
+          <t>-16,89; 34,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,79; -6,76</t>
+          <t>-57,51; -4,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,0; -9,03</t>
+          <t>-61,04; -8,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 51,08</t>
+          <t>-14,5; 50,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 78,34</t>
+          <t>-27,83; 71,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,68; 5,54</t>
+          <t>-32,08; 7,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 32,6</t>
+          <t>-9,08; 31,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 43,76</t>
+          <t>-30,36; 47,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 3,41</t>
+          <t>-22,55; 5,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 17,05</t>
+          <t>-8,9; 18,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 19,06</t>
+          <t>-6,5; 20,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 22,49</t>
+          <t>-8,97; 24,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 29,43</t>
+          <t>-2,07; 29,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 34,24</t>
+          <t>8,13; 33,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 9,76</t>
+          <t>-12,96; 8,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 18,87</t>
+          <t>-2,78; 18,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,57; 23,92</t>
+          <t>3,5; 23,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 7,32</t>
+          <t>-38,23; 10,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 34,92</t>
+          <t>-14,57; 38,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 37,66</t>
+          <t>-10,69; 43,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 57,93</t>
+          <t>-17,43; 64,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 77,42</t>
+          <t>-2,95; 75,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,06; 89,34</t>
+          <t>14,9; 86,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 20,51</t>
+          <t>-23,77; 18,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 39,78</t>
+          <t>-4,61; 40,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 50,96</t>
+          <t>6,02; 48,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 10,3</t>
+          <t>-4,68; 10,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 13,99</t>
+          <t>0,07; 14,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 16,46</t>
+          <t>1,59; 16,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 9,21</t>
+          <t>-10,06; 8,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,56; 24,63</t>
+          <t>6,34; 24,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 25,38</t>
+          <t>4,7; 25,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 7,42</t>
+          <t>-4,55; 7,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,49; 16,13</t>
+          <t>4,89; 16,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,64; 17,91</t>
+          <t>5,54; 17,43</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 20,97</t>
+          <t>-8,45; 21,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 27,9</t>
+          <t>0,2; 29,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2,88; 33,9</t>
+          <t>2,79; 33,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 19,86</t>
+          <t>-17,56; 18,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,58; 54,02</t>
+          <t>10,71; 51,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,3; 54,0</t>
+          <t>7,51; 52,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 15,19</t>
+          <t>-8,52; 16,0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,28; 32,51</t>
+          <t>9,09; 32,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,6; 36,72</t>
+          <t>10,16; 35,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6904-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6904-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,47</t>
+          <t>26,04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,83</t>
+          <t>-4,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,82</t>
+          <t>14,73</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 24,43</t>
+          <t>-8,74; 22,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 17,05</t>
+          <t>-17,1; 19,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 39,78</t>
+          <t>9,78; 39,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 21,6</t>
+          <t>-26,96; 20,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 28,04</t>
+          <t>-17,74; 27,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 16,35</t>
+          <t>-23,26; 15,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 18,11</t>
+          <t>-9,23; 18,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 18,06</t>
+          <t>-11,8; 17,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 26,79</t>
+          <t>2,59; 26,54</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-5,91%</t>
+          <t>-6,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 59,08</t>
+          <t>-15,12; 57,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 37,74</t>
+          <t>-29,49; 44,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,99; 97,96</t>
+          <t>17,31; 98,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 43,54</t>
+          <t>-37,07; 39,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 57,08</t>
+          <t>-22,79; 54,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 33,56</t>
+          <t>-31,23; 29,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 38,8</t>
+          <t>-15,15; 40,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 36,66</t>
+          <t>-19,24; 36,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 58,08</t>
+          <t>4,31; 58,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,37</t>
+          <t>17,09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,88</t>
+          <t>19,23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,9</t>
+          <t>17,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 23,64</t>
+          <t>-2,83; 23,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 30,57</t>
+          <t>3,68; 30,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 28,56</t>
+          <t>3,38; 28,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 30,37</t>
+          <t>-6,18; 32,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 42,95</t>
+          <t>4,8; 42,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 34,79</t>
+          <t>3,0; 33,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 21,47</t>
+          <t>-0,4; 21,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 31,11</t>
+          <t>8,17; 30,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 26,52</t>
+          <t>7,89; 26,66</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 54,46</t>
+          <t>-4,68; 58,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 73,28</t>
+          <t>6,91; 71,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 68,98</t>
+          <t>6,37; 69,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 92,67</t>
+          <t>-11,94; 101,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,75; 137,5</t>
+          <t>10,43; 132,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 116,25</t>
+          <t>5,45; 109,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 51,74</t>
+          <t>-1,0; 52,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,59; 77,11</t>
+          <t>15,99; 74,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 65,61</t>
+          <t>15,14; 65,37</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-19,04</t>
+          <t>-8,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>-10,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>-8,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 16,85</t>
+          <t>-15,69; 16,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 16,72</t>
+          <t>-12,27; 15,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,15; -1,72</t>
+          <t>-25,82; 8,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,21; -4,2</t>
+          <t>-43,65; -3,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 25,65</t>
+          <t>-9,66; 25,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 32,73</t>
+          <t>-29,5; 7,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 3,89</t>
+          <t>-21,41; 2,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 16,16</t>
+          <t>-5,49; 16,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 23,73</t>
+          <t>-20,44; 3,83</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-34,0%</t>
+          <t>-15,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>-17,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,27%</t>
+          <t>-14,42%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 33,49</t>
+          <t>-25,78; 33,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 34,89</t>
+          <t>-19,21; 32,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,51; -4,06</t>
+          <t>-42,49; 17,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,04; -8,15</t>
+          <t>-59,91; -4,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 50,73</t>
+          <t>-12,91; 50,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 71,01</t>
+          <t>-40,2; 13,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 7,38</t>
+          <t>-34,05; 5,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 31,92</t>
+          <t>-8,57; 31,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 47,49</t>
+          <t>-32,28; 7,3</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>7,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,14</t>
+          <t>19,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,12</t>
+          <t>12,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 5,1</t>
+          <t>-23,17; 4,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 18,42</t>
+          <t>-9,32; 17,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 20,58</t>
+          <t>-6,04; 20,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 24,86</t>
+          <t>-11,49; 23,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 29,24</t>
+          <t>-2,64; 30,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,13; 33,92</t>
+          <t>6,75; 32,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 8,94</t>
+          <t>-13,27; 8,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 18,55</t>
+          <t>-2,03; 18,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 23,0</t>
+          <t>3,76; 21,78</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 10,12</t>
+          <t>-38,89; 8,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 38,24</t>
+          <t>-16,14; 34,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 43,55</t>
+          <t>-10,26; 42,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 64,72</t>
+          <t>-20,59; 59,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 75,12</t>
+          <t>-5,22; 76,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,9; 86,93</t>
+          <t>12,22; 87,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 18,28</t>
+          <t>-24,12; 18,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 40,1</t>
+          <t>-3,04; 40,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,02; 48,91</t>
+          <t>6,64; 46,64</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,54</t>
+          <t>9,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,35</t>
+          <t>10,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 10,44</t>
+          <t>-4,44; 10,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 14,69</t>
+          <t>0,59; 15,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 16,34</t>
+          <t>3,99; 18,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 8,83</t>
+          <t>-9,82; 9,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,34; 24,1</t>
+          <t>5,95; 24,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,7; 25,75</t>
+          <t>0,39; 17,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 7,75</t>
+          <t>-4,35; 7,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,89; 16,14</t>
+          <t>4,77; 16,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,54; 17,43</t>
+          <t>4,77; 15,4</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 21,19</t>
+          <t>-8,12; 21,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,2; 29,9</t>
+          <t>1,06; 30,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2,79; 33,37</t>
+          <t>7,19; 37,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 18,63</t>
+          <t>-17,65; 19,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,71; 51,4</t>
+          <t>10,39; 52,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,51; 52,87</t>
+          <t>0,69; 36,95</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 16,0</t>
+          <t>-7,96; 14,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,09; 32,63</t>
+          <t>9,31; 32,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,16; 35,26</t>
+          <t>8,84; 31,3</t>
         </is>
       </c>
     </row>
